--- a/R_analysis/output/tables/Tabela_Indices_Desigualdade.xlsx
+++ b/R_analysis/output/tables/Tabela_Indices_Desigualdade.xlsx
@@ -399,7 +399,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gestacional</t>
+          <t>Gestational</t>
         </is>
       </c>
       <c r="B2">
@@ -427,7 +427,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Congênita</t>
+          <t>Congenital</t>
         </is>
       </c>
       <c r="B3">
